--- a/survey_templates/032_volunteer_coordination_efficiency_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/032_volunteer_coordination_efficiency_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_1</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_2</t>
+          <t>volunteer_coordinator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Volunteer Coordinator</t>
+          <t>Who is the primary volunteer coordinator?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3</t>
+          <t>frequency_of_meetings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frequency of Meetings</t>
+          <t>What is the frequency of meetings held for the volunteer program?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_4</t>
+          <t>tools_and_resources</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Volunteer Management Tools</t>
+          <t>What tools and resources are used for volunteer management?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_5</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time Management</t>
+          <t>What is the time management process like?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_6</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>How is communication handled for the volunteer program?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_7</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>What kind of training is provided for volunteers?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_8</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>What type of feedback is received from volunteers?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_9</t>
+          <t>coordination</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Coordination</t>
+          <t>Who is responsible for coordination?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_10</t>
+          <t>reporting_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>What is the reporting frequency for the volunteer program?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_11</t>
+          <t>coordination_tools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>What tools and resources are utilized for coordination and reporting?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12</t>
+          <t>communication_coordination</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frequency of Reporting</t>
+          <t>How is communication handled between coordinators?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_13</t>
+          <t>coordinator_training</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tools and Resources</t>
+          <t>What kind of training is provided for coordinators?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_14</t>
+          <t>feedback_coordinators</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>What type of feedback is received from coordinators?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_15</t>
+          <t>meetings_frequency</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>What is the frequency of meetings for coordinators?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_16</t>
+          <t>meetings_tools</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>What tools and resources are utilized for meetings?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_17</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coordination</t>
+          <t>How is reporting handled?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_18</t>
+          <t>overall_coordination</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>What is the overall experience with coordination?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_19</t>
+          <t>meeting_time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>At what time of day are meetings held?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20</t>
+          <t>last_report</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frequency of Reporting</t>
+          <t>On what date was the last report generated?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_21</t>
+          <t>reporting_frequency_volunteers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tools and Resources</t>
+          <t>Reporting Frequency Volunteers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_22</t>
+          <t>tools_volunteers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>What tools and resources are utilized for volunteers?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_23</t>
+          <t>feedback_volunteers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Feedback Volunteers</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_24</t>
+          <t>volunteer_training</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Volunteer Training</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,17 +1067,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_25</t>
+          <t>overall_volunteer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Meetings</t>
+          <t>What is the overall experience with the volunteer program?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,476 +1126,612 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_2_choices</t>
+          <t>volunteer_coordinator_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_2_choices</t>
+          <t>volunteer_coordinator_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_2_choices</t>
+          <t>volunteer_coordinator_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tertiary'}</t>
+          <t>Tertiary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_2_choices</t>
+          <t>volunteer_coordinator_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3_choices</t>
+          <t>frequency_of_meetings_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3_choices</t>
+          <t>frequency_of_meetings_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3_choices</t>
+          <t>frequency_of_meetings_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3_choices</t>
+          <t>frequency_of_meetings_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_3_choices</t>
+          <t>frequency_of_meetings_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_4_choices</t>
+          <t>tools_and_resources_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_4_choices</t>
+          <t>tools_and_resources_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spreadsheets'}</t>
+          <t>spreadsheets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spreadsheets'}</t>
+          <t>Spreadsheets</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_4_choices</t>
+          <t>tools_and_resources_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_12_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_13_choices</t>
+          <t>coordination_tools_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_13_choices</t>
+          <t>coordination_tools_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spreadsheets'}</t>
+          <t>spreadsheets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spreadsheets'}</t>
+          <t>Spreadsheets</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_13_choices</t>
+          <t>coordination_tools_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20_choices</t>
+          <t>meetings_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20_choices</t>
+          <t>meetings_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20_choices</t>
+          <t>meetings_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20_choices</t>
+          <t>meetings_frequency_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_20_choices</t>
+          <t>meetings_frequency_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_21_choices</t>
+          <t>meetings_tools_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_21_choices</t>
+          <t>meetings_tools_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spreadsheets'}</t>
+          <t>spreadsheets</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spreadsheets'}</t>
+          <t>Spreadsheets</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>volunteer_coordination_efficiency_form_21_choices</t>
+          <t>meetings_tools_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>reporting_frequency_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>reporting_frequency_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>reporting_frequency_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>reporting_frequency_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>reporting_frequency_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tools_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tools_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>spreadsheets</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Spreadsheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tools_volunteers_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
